--- a/Output/triple_all_interactions_combined.xlsx
+++ b/Output/triple_all_interactions_combined.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">-</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.544 (1.618)</t>
+    <t xml:space="preserve">-0.776 (1.614)</t>
   </si>
   <si>
     <t xml:space="preserve">post_share_1956_1978</t>
@@ -71,7 +71,10 @@
     <t xml:space="preserve">+</t>
   </si>
   <si>
-    <t xml:space="preserve">8.367 (6.253)</t>
+    <t xml:space="preserve">9.328 (6.268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+*</t>
   </si>
   <si>
     <t xml:space="preserve">post_x</t>
@@ -86,7 +89,7 @@
     <t xml:space="preserve">+**</t>
   </si>
   <si>
-    <t xml:space="preserve">0.021 (0.016)</t>
+    <t xml:space="preserve">0.019 (0.016)</t>
   </si>
   <si>
     <t xml:space="preserve">post_x_share_1936_1955</t>
@@ -98,7 +101,7 @@
     <t xml:space="preserve">-0.000 (0.034)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.013 (0.039)</t>
+    <t xml:space="preserve">0.018 (0.039)</t>
   </si>
   <si>
     <t xml:space="preserve">post_x_share_1956_1978</t>
@@ -110,7 +113,10 @@
     <t xml:space="preserve">-0.130 (0.125)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.195 (0.149)</t>
+    <t xml:space="preserve">-0.218 (0.149)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-*</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_hombre</t>
@@ -119,241 +125,238 @@
     <t xml:space="preserve">-1.637 (1.205)</t>
   </si>
   <si>
-    <t xml:space="preserve">-2.037 (1.344)</t>
+    <t xml:space="preserve">-2.492* (1.340)</t>
   </si>
   <si>
     <t xml:space="preserve">4.003 (4.405)</t>
   </si>
   <si>
-    <t xml:space="preserve">4.179 (5.218)</t>
+    <t xml:space="preserve">5.657 (5.281)</t>
   </si>
   <si>
     <t xml:space="preserve">-1.027 (1.141)</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.069 (1.248)</t>
+    <t xml:space="preserve">-1.431 (1.104)</t>
   </si>
   <si>
     <t xml:space="preserve">3.303 (2.402)</t>
   </si>
   <si>
-    <t xml:space="preserve">4.085 (2.686)</t>
+    <t xml:space="preserve">5.015* (2.681)</t>
   </si>
   <si>
     <t xml:space="preserve">-7.793 (8.868)</t>
   </si>
   <si>
-    <t xml:space="preserve">-8.166 (10.565)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mun_pre_all_share_rural</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.019 (0.035)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.011 (0.037)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.007 (0.101)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.017 (0.115)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.092** (0.041)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.090 (0.054)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.048 (0.070)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.073 (0.066)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893*** (0.311)</t>
+    <t xml:space="preserve">-11.121 (10.699)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">popdensgeo2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.036 (0.062)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.035 (0.069)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.446 (0.282)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431 (0.321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006 (0.008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010 (0.010)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.007 (0.012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.010 (0.014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.033 (0.041)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.033 (0.048)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mun_pre_all_share_desempleado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.094 (0.087)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.176** (0.085)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113 (0.359)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371 (0.396)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.352 (0.544)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.693 (0.496)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.437 (1.345)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.519* (1.305)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137 (5.436)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.753 (5.597)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mun_pre_all_share_en_pareja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470** (0.181)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492*** (0.159)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.186** (0.563)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.243* (0.651)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.222 (0.202)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356* (0.203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.868*** (0.319)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.945*** (0.273)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.402** (1.025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.495** (1.162)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mun_pre_all_mean_educ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263 (0.245)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.364 (0.231)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.339 (1.130)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.466 (1.066)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.032** (0.013)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.031* (0.017)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.028 (0.023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.040* (0.022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.098 (0.102)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.109 (0.098)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mun_pre_all_mean_izq_der</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115 (0.691)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.180 (0.704)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.486 (1.937)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.310 (2.259)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.039* (0.022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.041 (0.026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.021 (0.125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.034 (0.130)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108 (0.357)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.079 (0.423)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mun_pre_all_share_interes_pol_mucho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.080 (0.079)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.067 (0.072)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506* (0.293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.760*** (0.282)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.900*** (0.287)</t>
   </si>
   <si>
     <t xml:space="preserve">+***</t>
   </si>
   <si>
-    <t xml:space="preserve">1.088*** (0.290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mun_pre_all_share_desempleado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.094 (0.087)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.186** (0.088)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113 (0.359)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381 (0.396)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.352 (0.544)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.839 (0.542)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.437 (1.345)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.632* (1.349)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137 (5.436)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.931 (5.812)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mun_pre_all_share_en_pareja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470** (0.181)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468** (0.183)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.186** (0.563)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.125* (0.637)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.222 (0.202)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356* (0.209)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.868*** (0.319)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.897*** (0.326)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.402** (1.025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.284* (1.166)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mun_pre_all_mean_educ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263 (0.245)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433** (0.204)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.339 (1.130)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.168 (0.954)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.032** (0.013)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.028* (0.016)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.028 (0.023)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.046** (0.020)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.098 (0.102)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.080 (0.087)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mun_pre_all_mean_izq_der</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115 (0.691)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.180 (0.774)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.486 (1.937)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246 (2.644)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.039* (0.022)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.033 (0.025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.021 (0.125)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.034 (0.142)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108 (0.357)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.032 (0.493)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mun_pre_all_share_interes_pol_mucho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.080 (0.079)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.087 (0.065)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506* (0.293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.739*** (0.239)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900*** (0.287)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860** (0.324)</t>
+    <t xml:space="preserve">0.838** (0.334)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.575 (0.543)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.665 (0.474)</t>
+    <t xml:space="preserve">-0.536 (0.512)</t>
   </si>
   <si>
     <t xml:space="preserve">-2.034 (1.770)</t>
   </si>
   <si>
-    <t xml:space="preserve">-3.007* (1.553)</t>
+    <t xml:space="preserve">-3.299* (1.734)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_voto_blanco_nulo</t>
@@ -362,31 +365,31 @@
     <t xml:space="preserve">-0.060 (0.185)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.107 (0.190)</t>
+    <t xml:space="preserve">-0.101 (0.190)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.008 (0.704)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.041 (0.728)</t>
+    <t xml:space="preserve">0.005 (0.692)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.122 (0.357)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.014 (0.328)</t>
+    <t xml:space="preserve">0.008 (0.333)</t>
   </si>
   <si>
     <t xml:space="preserve">0.408 (1.283)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.651 (1.300)</t>
+    <t xml:space="preserve">0.624 (1.278)</t>
   </si>
   <si>
     <t xml:space="preserve">1.815 (5.587)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.454 (5.506)</t>
+    <t xml:space="preserve">1.821 (5.230)</t>
   </si>
 </sst>
 </file>
@@ -793,7 +796,7 @@
         <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" t="n">
         <v>7467</v>
@@ -807,19 +810,19 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
         <v>18</v>
@@ -836,19 +839,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
         <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
@@ -865,22 +868,22 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H6" t="n">
         <v>7467</v>
@@ -891,7 +894,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -900,13 +903,13 @@
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -920,7 +923,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -929,13 +932,13 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
         <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
         <v>18</v>
@@ -949,22 +952,22 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -978,22 +981,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
         <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
         <v>18</v>
@@ -1007,22 +1010,22 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -1036,7 +1039,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -1045,19 +1048,19 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="I12" t="n">
         <v>7412</v>
@@ -1065,7 +1068,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
@@ -1074,19 +1077,19 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H13" t="n">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="I13" t="n">
         <v>7412</v>
@@ -1094,28 +1097,28 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E14" t="s">
         <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H14" t="n">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="I14" t="n">
         <v>7412</v>
@@ -1123,28 +1126,28 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G15" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="I15" t="n">
         <v>7412</v>
@@ -1152,28 +1155,28 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="F16" t="s">
         <v>56</v>
       </c>
       <c r="G16" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="H16" t="n">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="I16" t="n">
         <v>7412</v>
@@ -1242,10 +1245,10 @@
         <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
         <v>63</v>
@@ -1257,7 +1260,7 @@
         <v>64</v>
       </c>
       <c r="G19" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="H19" t="n">
         <v>7467</v>
@@ -1271,10 +1274,10 @@
         <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
         <v>65</v>
@@ -1286,7 +1289,7 @@
         <v>66</v>
       </c>
       <c r="G20" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="H20" t="n">
         <v>7467</v>
@@ -1300,19 +1303,19 @@
         <v>57</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
         <v>68</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s">
-        <v>69</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1326,7 +1329,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
@@ -1335,16 +1338,16 @@
         <v>11</v>
       </c>
       <c r="D22" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" t="s">
         <v>71</v>
       </c>
-      <c r="E22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" t="s">
-        <v>72</v>
-      </c>
       <c r="G22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" t="n">
         <v>7467</v>
@@ -1355,7 +1358,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
@@ -1364,13 +1367,13 @@
         <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
         <v>60</v>
       </c>
       <c r="F23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G23" t="s">
         <v>60</v>
@@ -1384,22 +1387,22 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" t="s">
         <v>75</v>
-      </c>
-      <c r="E24" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" t="s">
-        <v>76</v>
       </c>
       <c r="G24" t="s">
         <v>18</v>
@@ -1413,25 +1416,25 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E25" t="s">
         <v>60</v>
       </c>
       <c r="F25" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" t="s">
         <v>78</v>
-      </c>
-      <c r="G25" t="s">
-        <v>60</v>
       </c>
       <c r="H25" t="n">
         <v>7467</v>
@@ -1442,25 +1445,25 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
         <v>79</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
         <v>80</v>
       </c>
       <c r="G26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" t="n">
         <v>7467</v>
@@ -1532,10 +1535,10 @@
         <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D29" t="s">
         <v>86</v>
@@ -1561,10 +1564,10 @@
         <v>81</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
         <v>88</v>
@@ -1590,10 +1593,10 @@
         <v>81</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
         <v>90</v>
@@ -1677,10 +1680,10 @@
         <v>92</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D34" t="s">
         <v>97</v>
@@ -1706,10 +1709,10 @@
         <v>92</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D35" t="s">
         <v>99</v>
@@ -1735,10 +1738,10 @@
         <v>92</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D36" t="s">
         <v>101</v>
@@ -1750,7 +1753,7 @@
         <v>102</v>
       </c>
       <c r="G36" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H36" t="n">
         <v>7467</v>
@@ -1808,7 +1811,7 @@
         <v>107</v>
       </c>
       <c r="G38" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="H38" t="n">
         <v>7467</v>
@@ -1822,22 +1825,22 @@
         <v>103</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
       </c>
       <c r="E39" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="F39" t="s">
+        <v>110</v>
+      </c>
+      <c r="G39" t="s">
         <v>109</v>
-      </c>
-      <c r="G39" t="s">
-        <v>55</v>
       </c>
       <c r="H39" t="n">
         <v>7467</v>
@@ -1851,19 +1854,19 @@
         <v>103</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E40" t="s">
         <v>13</v>
       </c>
       <c r="F40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G40" t="s">
         <v>13</v>
@@ -1880,22 +1883,22 @@
         <v>103</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E41" t="s">
         <v>13</v>
       </c>
       <c r="F41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G41" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H41" t="n">
         <v>7467</v>
@@ -1906,7 +1909,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
@@ -1915,13 +1918,13 @@
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E42" t="s">
         <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G42" t="s">
         <v>13</v>
@@ -1935,7 +1938,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
         <v>15</v>
@@ -1944,13 +1947,13 @@
         <v>16</v>
       </c>
       <c r="D43" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E43" t="s">
         <v>13</v>
       </c>
       <c r="F43" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G43" t="s">
         <v>13</v>
@@ -1964,22 +1967,22 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D44" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E44" t="s">
         <v>13</v>
       </c>
       <c r="F44" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G44" t="s">
         <v>18</v>
@@ -1993,22 +1996,22 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E45" t="s">
         <v>18</v>
       </c>
       <c r="F45" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G45" t="s">
         <v>18</v>
@@ -2022,22 +2025,22 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E46" t="s">
         <v>18</v>
       </c>
       <c r="F46" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G46" t="s">
         <v>18</v>
